--- a/src/test/resources/testdata/CourseData.xlsx
+++ b/src/test/resources/testdata/CourseData.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
-    <t>Extracted: 23-May-2026 20:07:54</t>
+    <t>Extracted: 25-May-2026 10:27:35</t>
   </si>
   <si>
     <t>S.No</t>
